--- a/doctool/test/auto/scenario32/システム機能設計書_サンプル_S32_expected.xlsx
+++ b/doctool/test/auto/scenario32/システム機能設計書_サンプル_S32_expected.xlsx
@@ -5,40 +5,39 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJ\01.Nablarch\repo\review-support-tool\doctool\test\temp_dir\scenario32\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJ\01.Nablarch\repo\review-support-tool\doctool\test\temp_dir\scenario31\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE4E4BC4-A4AF-4FFD-9A2A-EA0424414DC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5EAFB83-60F4-4ADD-B58C-E7C5C28DB933}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="エラーシート" sheetId="11" r:id="rId1"/>
-    <sheet name="レビュー結果1回目" sheetId="10" r:id="rId2"/>
-    <sheet name="表紙" sheetId="1" r:id="rId3"/>
-    <sheet name="変更履歴" sheetId="2" r:id="rId4"/>
-    <sheet name="目次" sheetId="3" r:id="rId5"/>
-    <sheet name="1.  画面取引定義" sheetId="4" r:id="rId6"/>
-    <sheet name="2. WA1020101(プロジェクト登録画面)" sheetId="5" r:id="rId7"/>
-    <sheet name="3. WA1020102(プロジェクト登録確認画面)" sheetId="6" r:id="rId8"/>
-    <sheet name="4. WA1020103(プロジェクト登録完了画面)" sheetId="7" r:id="rId9"/>
-    <sheet name="データ" sheetId="8" state="hidden" r:id="rId10"/>
+    <sheet name="レビュー結果1回目" sheetId="11" r:id="rId1"/>
+    <sheet name="表紙" sheetId="1" r:id="rId2"/>
+    <sheet name="変更履歴" sheetId="2" r:id="rId3"/>
+    <sheet name="目次" sheetId="3" r:id="rId4"/>
+    <sheet name="1.  画面取引定義" sheetId="4" r:id="rId5"/>
+    <sheet name="2. WA1020101(プロジェクト登録画面)" sheetId="5" r:id="rId6"/>
+    <sheet name="3. WA1020102(プロジェクト登録確認画面)" sheetId="6" r:id="rId7"/>
+    <sheet name="4. WA1020103(プロジェクト登録完了画面)" sheetId="7" r:id="rId8"/>
+    <sheet name="データ" sheetId="8" state="hidden" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_Toc46209822" localSheetId="5">'1.  画面取引定義'!$B$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'1.  画面取引定義'!$A$1:$AI$21</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'2. WA1020101(プロジェクト登録画面)'!$A$1:$AI$180</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'3. WA1020102(プロジェクト登録確認画面)'!$A$1:$AI$136</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'4. WA1020103(プロジェクト登録完了画面)'!$A$1:$AI$68</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">データ!$A$1:$E$15</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">レビュー結果1回目!$A$1:$K$20</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">表紙!$A$1:$S$39</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">変更履歴!$A$1:$AI$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">目次!$A$1:$AI$33</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'1.  画面取引定義'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'2. WA1020101(プロジェクト登録画面)'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'3. WA1020102(プロジェクト登録確認画面)'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'4. WA1020103(プロジェクト登録完了画面)'!$1:$4</definedName>
+    <definedName name="_Toc46209822" localSheetId="4">'1.  画面取引定義'!$B$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'1.  画面取引定義'!$A$1:$AI$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'2. WA1020101(プロジェクト登録画面)'!$A$1:$AI$180</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'3. WA1020102(プロジェクト登録確認画面)'!$A$1:$AI$136</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'4. WA1020103(プロジェクト登録完了画面)'!$A$1:$AI$68</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">データ!$A$1:$E$15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">レビュー結果1回目!$A$1:$Q$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">表紙!$A$1:$S$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">変更履歴!$A$1:$AI$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">目次!$A$1:$AI$33</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'1.  画面取引定義'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'2. WA1020101(プロジェクト登録画面)'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'3. WA1020102(プロジェクト登録確認画面)'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'4. WA1020103(プロジェクト登録完了画面)'!$1:$4</definedName>
     <definedName name="引継項目格納先">データ!$B$2:$B$2</definedName>
     <definedName name="画面項目種類">データ!$A$2:$A$14</definedName>
     <definedName name="種別一覧">データ!$C$2:$C$7</definedName>
@@ -66,7 +65,7 @@
     <author>山田　太郎</author>
   </authors>
   <commentList>
-    <comment ref="E35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="E65" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
@@ -75,8 +74,36 @@
             <family val="1"/>
             <charset val="128"/>
           </rPr>
-          <t>山田　太郎:g
-gカテゴリの指摘コメント。</t>
+          <t>山田　太郎:m
+mカテゴリの指摘コメント。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E70" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="ＭＳ 明朝"/>
+            <family val="1"/>
+            <charset val="128"/>
+          </rPr>
+          <t>山田　太郎:n
+nカテゴリの指摘コメント。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E75" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="ＭＳ 明朝"/>
+            <family val="1"/>
+            <charset val="128"/>
+          </rPr>
+          <t>山田　太郎:o
+oカテゴリの指摘コメント。</t>
         </r>
       </text>
     </comment>
@@ -200,7 +227,77 @@
         </r>
       </text>
     </comment>
-    <comment ref="A71" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000008000000}">
+    <comment ref="E66" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000008000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="ＭＳ 明朝"/>
+            <family val="1"/>
+            <charset val="128"/>
+          </rPr>
+          <t>山田　太郎:g
+疑問点・確認の指摘例（カテゴリg）。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E67" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000009000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="ＭＳ 明朝"/>
+            <family val="1"/>
+            <charset val="128"/>
+          </rPr>
+          <t>山田　太郎:h
+改善要望の指摘例（カテゴリh）。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E68" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000A000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="ＭＳ 明朝"/>
+            <family val="1"/>
+            <charset val="128"/>
+          </rPr>
+          <t>山田　太郎:i
+仕様変更の指摘例（カテゴリi）。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E69" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000B000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="ＭＳ 明朝"/>
+            <family val="1"/>
+            <charset val="128"/>
+          </rPr>
+          <t>山田　太郎:j
+テスト項目漏れの指摘例（カテゴリj）。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E70" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000C000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="ＭＳ 明朝"/>
+            <family val="1"/>
+            <charset val="128"/>
+          </rPr>
+          <t>山田　太郎:k
+テスト漏れの指摘例（カテゴリk）。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A71" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000D000000}">
       <text>
         <r>
           <rPr>
@@ -214,12 +311,26 @@
         </r>
       </text>
     </comment>
+    <comment ref="E71" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000E000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="ＭＳ 明朝"/>
+            <family val="1"/>
+            <charset val="128"/>
+          </rPr>
+          <t>山田　太郎:l
+その他の指摘例（カテゴリl）。</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="366">
   <si>
     <t>第１．２版</t>
   </si>
@@ -1153,6 +1264,34 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
+    <t>f</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>g</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>h</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>i</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>j</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>k</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>l</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
     <t>対応状況</t>
     <rPh sb="0" eb="2">
       <t>タイオウ</t>
@@ -1183,6 +1322,34 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
+    <t>22_記述誤り</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>91_疑問点、確認</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>92_改善要望</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>93_仕様変更</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>94_テスト項目漏れ</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>95_テスト漏れ</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>96_その他</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
     <t>計</t>
     <rPh sb="0" eb="1">
       <t>ケイ</t>
@@ -1262,16 +1429,13 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>システム機能設計書_サンプル_S32</t>
+    <t>システム機能設計書_サンプル_S31</t>
+  </si>
+  <si>
+    <t>B5</t>
   </si>
   <si>
     <t>山田　太郎</t>
-  </si>
-  <si>
-    <t>未</t>
-  </si>
-  <si>
-    <t>B5</t>
   </si>
   <si>
     <t>a</t>
@@ -1280,6 +1444,9 @@
     <t>レビュー指摘コメントの例。
 自動で挿入される名前とコロンの直後に指摘分類をa～iで書く。
 ※レビュー日時を書く場合はコロンの直後に*を書く。</t>
+  </si>
+  <si>
+    <t>未</t>
   </si>
   <si>
     <t>E60</t>
@@ -1327,27 +1494,115 @@
     <t>設計・ドキュメント規約違反の指摘例（カテゴリe）。</t>
   </si>
   <si>
-    <t>＜エラー＞</t>
+    <t>E65</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>記述誤りの指摘例（カテゴリf）。</t>
+  </si>
+  <si>
+    <t>E66</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>疑問点・確認の指摘例（カテゴリg）。</t>
+  </si>
+  <si>
+    <t>E67</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>改善要望の指摘例（カテゴリh）。</t>
+  </si>
+  <si>
+    <t>E68</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>仕様変更の指摘例（カテゴリi）。</t>
+  </si>
+  <si>
+    <t>E69</t>
+  </si>
+  <si>
+    <t>j</t>
+  </si>
+  <si>
+    <t>テスト項目漏れの指摘例（カテゴリj）。</t>
+  </si>
+  <si>
+    <t>E70</t>
+  </si>
+  <si>
+    <t>k</t>
+  </si>
+  <si>
+    <t>テスト漏れの指摘例（カテゴリk）。</t>
+  </si>
+  <si>
+    <t>E71</t>
+  </si>
+  <si>
+    <t>l</t>
+  </si>
+  <si>
+    <t>その他の指摘例（カテゴリl）。</t>
+  </si>
+  <si>
+    <t>m</t>
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>エラー内容</t>
-    <rPh sb="3" eb="5">
-      <t>ナイヨウ</t>
-    </rPh>
+    <t>n</t>
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>未登録の指摘分類エイリアスが記入されています: g</t>
-  </si>
-  <si>
-    <t>変更履歴'!$E$35</t>
-  </si>
-  <si>
-    <t>未登録の指摘分類エイリアスが記入されています: f</t>
-  </si>
-  <si>
-    <t>2. WA1020101(プロジェクト登録画面)'!$E$65</t>
+    <t>o</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>97_性能問題</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>98_セキュリティ</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>99_その他2</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>変更履歴</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>mカテゴリの指摘コメント。</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>nカテゴリの指摘コメント。</t>
+  </si>
+  <si>
+    <t>E75</t>
+  </si>
+  <si>
+    <t>o</t>
+  </si>
+  <si>
+    <t>oカテゴリの指摘コメント。</t>
   </si>
 </sst>
 </file>
@@ -2069,7 +2324,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="300">
+  <cellXfs count="302">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2772,6 +3027,9 @@
     <xf numFmtId="0" fontId="26" fillId="8" borderId="10" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" xfId="11" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2781,10 +3039,16 @@
     <xf numFmtId="178" fontId="22" fillId="9" borderId="10" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="22" fillId="9" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="8" borderId="10" xfId="11" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="22" fillId="9" borderId="10" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="22" fillId="9" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="178" fontId="22" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2829,10 +3093,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="11" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="5" quotePrefix="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
@@ -3269,227 +3529,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A1A1BFF-4E18-4DC8-AA87-423CB46718F1}">
-  <sheetPr codeName="ErrorSheetTemplate">
-    <tabColor theme="3" tint="0.59999389629810485"/>
-  </sheetPr>
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="1" max="1" width="105.1640625" style="287" customWidth="1"/>
-    <col min="2" max="2" width="42.1640625" style="262" customWidth="1"/>
-    <col min="3" max="16384" width="9.33203125" style="262"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A1" s="286" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A2" s="287" t="s">
-        <v>318</v>
-      </c>
-      <c r="B2" s="262" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A3" s="287" t="s">
-        <v>319</v>
-      </c>
-      <c r="B3" s="299" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A4" s="287" t="s">
-        <v>321</v>
-      </c>
-      <c r="B4" s="299" t="s">
-        <v>322</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="10"/>
-  <hyperlinks>
-    <hyperlink ref="B3" location="'変更履歴'!$E$35" display="'変更履歴'!$E$35" xr:uid="{8A580809-03AB-47A5-A143-EA15343C9AAD}"/>
-    <hyperlink ref="B4" location="'2. WA1020101(プロジェクト登録画面)'!$E$65" display="'2. WA1020101(プロジェクト登録画面)'!$E$65" xr:uid="{A39A4EB3-6313-457C-89D1-A61C2BF261B6}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <sheetPr codeName="Sheet6">
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="2" width="30.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.1640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A1" s="53" t="s">
-        <v>249</v>
-      </c>
-      <c r="B1" s="54" t="s">
-        <v>250</v>
-      </c>
-      <c r="C1" s="55" t="s">
-        <v>251</v>
-      </c>
-      <c r="D1" s="55" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A2" s="52" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="56" t="s">
-        <v>252</v>
-      </c>
-      <c r="C2" s="57" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="52" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A3" s="52" t="s">
-        <v>106</v>
-      </c>
-      <c r="B3" s="56" t="s">
-        <v>253</v>
-      </c>
-      <c r="C3" s="52" t="s">
-        <v>134</v>
-      </c>
-      <c r="D3" s="52" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A4" s="52" t="s">
-        <v>90</v>
-      </c>
-      <c r="B4" s="52" t="s">
-        <v>254</v>
-      </c>
-      <c r="C4" s="52" t="s">
-        <v>255</v>
-      </c>
-      <c r="D4" s="52" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A5" s="52" t="s">
-        <v>256</v>
-      </c>
-      <c r="B5" s="52" t="s">
-        <v>257</v>
-      </c>
-      <c r="C5" s="52" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A6" s="52" t="s">
-        <v>122</v>
-      </c>
-      <c r="C6" s="52" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A7" s="52" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="52" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A8" s="52" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A9" s="52" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A10" s="52" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A11" s="52" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A12" s="52" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A13" s="52" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A14" s="52" t="s">
-        <v>264</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="10"/>
-  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76FBF0C5-BFCB-43C2-853B-A9A84C41923B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AD5E0D3-F4C6-4381-9644-6AB1EF741361}">
   <sheetPr codeName="SheetTemplate">
     <tabColor indexed="44"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:AL30"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="262"/>
-    <col min="2" max="11" width="17.6640625" style="262" customWidth="1"/>
-    <col min="12" max="16" width="4.5" style="262" customWidth="1"/>
-    <col min="17" max="17" width="98.1640625" style="262" customWidth="1"/>
-    <col min="18" max="18" width="4.5" style="262" customWidth="1"/>
-    <col min="19" max="19" width="98.1640625" style="262" customWidth="1"/>
-    <col min="20" max="20" width="4.5" style="262" customWidth="1"/>
-    <col min="21" max="21" width="98.1640625" style="262" customWidth="1"/>
-    <col min="22" max="16384" width="9.33203125" style="262"/>
+    <col min="2" max="17" width="17.6640625" style="262" customWidth="1"/>
+    <col min="18" max="32" width="4.5" style="262" customWidth="1"/>
+    <col min="33" max="33" width="98.1640625" style="262" customWidth="1"/>
+    <col min="34" max="16384" width="9.33203125" style="262"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.15">
       <c r="A1" s="261" t="s">
         <v>265</v>
       </c>
-      <c r="L1" s="263"/>
-      <c r="Q1" s="264" t="s">
+      <c r="R1" s="263"/>
+      <c r="AG1" s="264" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.15">
       <c r="A2" s="262" t="s">
         <v>267</v>
       </c>
@@ -3500,9 +3564,9 @@
       <c r="G2" s="266"/>
       <c r="H2" s="266"/>
       <c r="I2" s="267"/>
-      <c r="L2" s="263"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R2" s="263"/>
+    </row>
+    <row r="3" spans="1:38" x14ac:dyDescent="0.15">
       <c r="A3" s="268" t="s">
         <v>269</v>
       </c>
@@ -3524,9 +3588,9 @@
         <v>274</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.15">
       <c r="A4" s="271" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="B4" s="271"/>
       <c r="C4" s="272">
@@ -3548,12 +3612,12 @@
         <v>200</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.15">
       <c r="A6" s="261" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.15">
       <c r="B7" s="276" t="s">
         <v>277</v>
       </c>
@@ -3569,228 +3633,496 @@
       <c r="F7" s="270" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" ht="27" x14ac:dyDescent="0.15">
+      <c r="G7" s="270" t="s">
+        <v>282</v>
+      </c>
+      <c r="H7" s="270" t="s">
+        <v>283</v>
+      </c>
+      <c r="I7" s="270" t="s">
+        <v>284</v>
+      </c>
+      <c r="J7" s="270" t="s">
+        <v>285</v>
+      </c>
+      <c r="K7" s="270" t="s">
+        <v>286</v>
+      </c>
+      <c r="L7" s="270" t="s">
+        <v>287</v>
+      </c>
+      <c r="M7" s="270" t="s">
+        <v>288</v>
+      </c>
+      <c r="N7" s="270" t="s">
+        <v>352</v>
+      </c>
+      <c r="O7" s="270" t="s">
+        <v>353</v>
+      </c>
+      <c r="P7" s="270" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="8" spans="1:38" ht="27" x14ac:dyDescent="0.15">
       <c r="A8" s="269" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="B8" s="277" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="C8" s="277" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="D8" s="277" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="E8" s="278" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="F8" s="277" t="s">
-        <v>287</v>
-      </c>
-      <c r="G8" s="279" t="s">
-        <v>288</v>
-      </c>
-      <c r="H8" s="280"/>
-      <c r="I8" s="280"/>
-      <c r="J8" s="280"/>
-      <c r="K8" s="280"/>
-      <c r="L8" s="280"/>
-      <c r="M8" s="280"/>
-      <c r="N8" s="280"/>
-      <c r="O8" s="280"/>
-      <c r="P8" s="280"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.15">
+        <v>294</v>
+      </c>
+      <c r="G8" s="277" t="s">
+        <v>295</v>
+      </c>
+      <c r="H8" s="277" t="s">
+        <v>296</v>
+      </c>
+      <c r="I8" s="277" t="s">
+        <v>297</v>
+      </c>
+      <c r="J8" s="278" t="s">
+        <v>298</v>
+      </c>
+      <c r="K8" s="278" t="s">
+        <v>299</v>
+      </c>
+      <c r="L8" s="278" t="s">
+        <v>300</v>
+      </c>
+      <c r="M8" s="278" t="s">
+        <v>301</v>
+      </c>
+      <c r="N8" s="278" t="s">
+        <v>355</v>
+      </c>
+      <c r="O8" s="278" t="s">
+        <v>356</v>
+      </c>
+      <c r="P8" s="278" t="s">
+        <v>357</v>
+      </c>
+      <c r="Q8" s="279" t="s">
+        <v>302</v>
+      </c>
+      <c r="R8" s="280"/>
+      <c r="S8" s="280"/>
+      <c r="T8" s="280"/>
+      <c r="U8" s="280"/>
+      <c r="V8" s="280"/>
+      <c r="W8" s="280"/>
+      <c r="X8" s="281"/>
+      <c r="Y8" s="281"/>
+      <c r="Z8" s="281"/>
+      <c r="AA8" s="281"/>
+      <c r="AB8" s="281"/>
+      <c r="AC8" s="281"/>
+      <c r="AD8" s="281"/>
+      <c r="AE8" s="281"/>
+      <c r="AF8" s="281"/>
+      <c r="AG8" s="281"/>
+      <c r="AH8" s="281"/>
+      <c r="AI8" s="281"/>
+      <c r="AJ8" s="281"/>
+      <c r="AK8" s="281"/>
+      <c r="AL8" s="281"/>
+    </row>
+    <row r="9" spans="1:38" x14ac:dyDescent="0.15">
       <c r="A9" s="269" t="s">
-        <v>289</v>
-      </c>
-      <c r="B9" s="281" t="str">
-        <f>IF(SUMIF($K15:$K20,$A9,L15:L20)=0,"",SUMIF($K15:$K20,$A9,L15:L20))</f>
+        <v>303</v>
+      </c>
+      <c r="B9" s="282" t="str">
+        <f>IF(SUMIF($K15:$K30,$A9,R15:R30)=0,"",SUMIF($K15:$K30,$A9,R15:R30))</f>
         <v/>
       </c>
-      <c r="C9" s="281" t="str">
-        <f>IF(SUMIF($K15:$K20,$A9,M15:M20)=0,"",SUMIF($K15:$K20,$A9,M15:M20))</f>
+      <c r="C9" s="282" t="str">
+        <f>IF(SUMIF($K15:$K30,$A9,S15:S30)=0,"",SUMIF($K15:$K30,$A9,S15:S30))</f>
         <v/>
       </c>
-      <c r="D9" s="281">
-        <f>IF(SUMIF($K15:$K20,$A9,N15:N20)=0,"",SUMIF($K15:$K20,$A9,N15:N20))</f>
+      <c r="D9" s="282">
+        <f>IF(SUMIF($K15:$K30,$A9,T15:T30)=0,"",SUMIF($K15:$K30,$A9,T15:T30))</f>
         <v>1</v>
       </c>
-      <c r="E9" s="281" t="str">
-        <f>IF(SUMIF($K15:$K20,$A9,O15:O20)=0,"",SUMIF($K15:$K20,$A9,O15:O20))</f>
+      <c r="E9" s="282" t="str">
+        <f>IF(SUMIF($K15:$K30,$A9,U15:U30)=0,"",SUMIF($K15:$K30,$A9,U15:U30))</f>
         <v/>
       </c>
-      <c r="F9" s="281" t="str">
-        <f>IF(SUMIF($K15:$K20,$A9,P15:P20)=0,"",SUMIF($K15:$K20,$A9,P15:P20))</f>
+      <c r="F9" s="282" t="str">
+        <f>IF(SUMIF($K15:$K30,$A9,V15:V30)=0,"",SUMIF($K15:$K30,$A9,V15:V30))</f>
         <v/>
       </c>
-      <c r="G9" s="282">
-        <f>SUM(B9:F9)</f>
+      <c r="G9" s="282" t="str">
+        <f>IF(SUMIF($K15:$K30,$A9,W15:W30)=0,"",SUMIF($K15:$K30,$A9,W15:W30))</f>
+        <v/>
+      </c>
+      <c r="H9" s="282" t="str">
+        <f>IF(SUMIF($K15:$K30,$A9,X15:X30)=0,"",SUMIF($K15:$K30,$A9,X15:X30))</f>
+        <v/>
+      </c>
+      <c r="I9" s="282" t="str">
+        <f>IF(SUMIF($K15:$K30,$A9,Y15:Y30)=0,"",SUMIF($K15:$K30,$A9,Y15:Y30))</f>
+        <v/>
+      </c>
+      <c r="J9" s="282" t="str">
+        <f>IF(SUMIF($K15:$K30,$A9,Z15:Z30)=0,"",SUMIF($K15:$K30,$A9,Z15:Z30))</f>
+        <v/>
+      </c>
+      <c r="K9" s="282" t="str">
+        <f>IF(SUMIF($K15:$K30,$A9,AA15:AA30)=0,"",SUMIF($K15:$K30,$A9,AA15:AA30))</f>
+        <v/>
+      </c>
+      <c r="L9" s="282" t="str">
+        <f>IF(SUMIF($K15:$K30,$A9,AB15:AB30)=0,"",SUMIF($K15:$K30,$A9,AB15:AB30))</f>
+        <v/>
+      </c>
+      <c r="M9" s="282" t="str">
+        <f>IF(SUMIF($K15:$K30,$A9,AC15:AC30)=0,"",SUMIF($K15:$K30,$A9,AC15:AC30))</f>
+        <v/>
+      </c>
+      <c r="N9" s="282" t="str">
+        <f>IF(SUMIF($K15:$K30,$A9,AD15:AD30)=0,"",SUMIF($K15:$K30,$A9,AD15:AD30))</f>
+        <v/>
+      </c>
+      <c r="O9" s="282" t="str">
+        <f>IF(SUMIF($K15:$K30,$A9,AE15:AE30)=0,"",SUMIF($K15:$K30,$A9,AE15:AE30))</f>
+        <v/>
+      </c>
+      <c r="P9" s="282" t="str">
+        <f>IF(SUMIF($K15:$K30,$A9,AF15:AF30)=0,"",SUMIF($K15:$K30,$A9,AF15:AF30))</f>
+        <v/>
+      </c>
+      <c r="Q9" s="283">
+        <f>SUM(B9:P9)</f>
         <v>1</v>
       </c>
-      <c r="H9" s="261"/>
-      <c r="I9" s="261"/>
-      <c r="J9" s="261"/>
-      <c r="K9" s="261"/>
-      <c r="L9" s="261"/>
-      <c r="M9" s="261"/>
-      <c r="N9" s="261"/>
-      <c r="O9" s="261"/>
-      <c r="P9" s="261"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="R9" s="284"/>
+      <c r="S9" s="284"/>
+      <c r="T9" s="284"/>
+      <c r="U9" s="284"/>
+      <c r="V9" s="284"/>
+      <c r="W9" s="284"/>
+      <c r="X9" s="261"/>
+      <c r="Y9" s="261"/>
+      <c r="Z9" s="261"/>
+      <c r="AA9" s="261"/>
+      <c r="AB9" s="261"/>
+      <c r="AC9" s="261"/>
+      <c r="AD9" s="261"/>
+      <c r="AE9" s="261"/>
+      <c r="AF9" s="261"/>
+      <c r="AG9" s="261"/>
+      <c r="AH9" s="261"/>
+      <c r="AI9" s="261"/>
+      <c r="AJ9" s="261"/>
+      <c r="AK9" s="261"/>
+      <c r="AL9" s="261"/>
+    </row>
+    <row r="10" spans="1:38" x14ac:dyDescent="0.15">
       <c r="A10" s="269" t="s">
-        <v>290</v>
-      </c>
-      <c r="B10" s="281">
-        <f>IF(SUMIF($K15:$K20,$A10,L15:L20)=0,"",SUMIF($K15:$K20,$A10,L15:L20))</f>
+        <v>304</v>
+      </c>
+      <c r="B10" s="282">
+        <f>IF(SUMIF($K15:$K30,$A10,R15:R30)=0,"",SUMIF($K15:$K30,$A10,R15:R30))</f>
         <v>1</v>
       </c>
-      <c r="C10" s="281">
-        <f>IF(SUMIF($K15:$K20,$A10,M15:M20)=0,"",SUMIF($K15:$K20,$A10,M15:M20))</f>
+      <c r="C10" s="282">
+        <f>IF(SUMIF($K15:$K30,$A10,S15:S30)=0,"",SUMIF($K15:$K30,$A10,S15:S30))</f>
         <v>1</v>
       </c>
-      <c r="D10" s="281" t="str">
-        <f>IF(SUMIF($K15:$K20,$A10,N15:N20)=0,"",SUMIF($K15:$K20,$A10,N15:N20))</f>
+      <c r="D10" s="282" t="str">
+        <f>IF(SUMIF($K15:$K30,$A10,T15:T30)=0,"",SUMIF($K15:$K30,$A10,T15:T30))</f>
         <v/>
       </c>
-      <c r="E10" s="281">
-        <f>IF(SUMIF($K15:$K20,$A10,O15:O20)=0,"",SUMIF($K15:$K20,$A10,O15:O20))</f>
+      <c r="E10" s="282">
+        <f>IF(SUMIF($K15:$K30,$A10,U15:U30)=0,"",SUMIF($K15:$K30,$A10,U15:U30))</f>
         <v>1</v>
       </c>
-      <c r="F10" s="281">
-        <f>IF(SUMIF($K15:$K20,$A10,P15:P20)=0,"",SUMIF($K15:$K20,$A10,P15:P20))</f>
+      <c r="F10" s="282">
+        <f>IF(SUMIF($K15:$K30,$A10,V15:V30)=0,"",SUMIF($K15:$K30,$A10,V15:V30))</f>
         <v>1</v>
       </c>
       <c r="G10" s="282">
-        <f>SUM(B10:F10)</f>
-        <v>4</v>
-      </c>
-      <c r="H10" s="261"/>
-      <c r="I10" s="261"/>
-      <c r="J10" s="261"/>
-      <c r="K10" s="261"/>
-      <c r="L10" s="261"/>
-      <c r="M10" s="261"/>
-      <c r="N10" s="261"/>
-      <c r="O10" s="261"/>
-      <c r="P10" s="261"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A11" s="283" t="s">
-        <v>288</v>
-      </c>
-      <c r="B11" s="284">
+        <f>IF(SUMIF($K15:$K30,$A10,W15:W30)=0,"",SUMIF($K15:$K30,$A10,W15:W30))</f>
+        <v>1</v>
+      </c>
+      <c r="H10" s="282">
+        <f>IF(SUMIF($K15:$K30,$A10,X15:X30)=0,"",SUMIF($K15:$K30,$A10,X15:X30))</f>
+        <v>1</v>
+      </c>
+      <c r="I10" s="282">
+        <f>IF(SUMIF($K15:$K30,$A10,Y15:Y30)=0,"",SUMIF($K15:$K30,$A10,Y15:Y30))</f>
+        <v>1</v>
+      </c>
+      <c r="J10" s="282">
+        <f>IF(SUMIF($K15:$K30,$A10,Z15:Z30)=0,"",SUMIF($K15:$K30,$A10,Z15:Z30))</f>
+        <v>1</v>
+      </c>
+      <c r="K10" s="282">
+        <f>IF(SUMIF($K15:$K30,$A10,AA15:AA30)=0,"",SUMIF($K15:$K30,$A10,AA15:AA30))</f>
+        <v>1</v>
+      </c>
+      <c r="L10" s="282">
+        <f>IF(SUMIF($K15:$K30,$A10,AB15:AB30)=0,"",SUMIF($K15:$K30,$A10,AB15:AB30))</f>
+        <v>1</v>
+      </c>
+      <c r="M10" s="282">
+        <f>IF(SUMIF($K15:$K30,$A10,AC15:AC30)=0,"",SUMIF($K15:$K30,$A10,AC15:AC30))</f>
+        <v>1</v>
+      </c>
+      <c r="N10" s="282">
+        <f>IF(SUMIF($K15:$K30,$A10,AD15:AD30)=0,"",SUMIF($K15:$K30,$A10,AD15:AD30))</f>
+        <v>1</v>
+      </c>
+      <c r="O10" s="282">
+        <f>IF(SUMIF($K15:$K30,$A10,AE15:AE30)=0,"",SUMIF($K15:$K30,$A10,AE15:AE30))</f>
+        <v>1</v>
+      </c>
+      <c r="P10" s="282">
+        <f>IF(SUMIF($K15:$K30,$A10,AF15:AF30)=0,"",SUMIF($K15:$K30,$A10,AF15:AF30))</f>
+        <v>1</v>
+      </c>
+      <c r="Q10" s="283">
+        <f>SUM(B10:P10)</f>
+        <v>14</v>
+      </c>
+      <c r="R10" s="284"/>
+      <c r="S10" s="284"/>
+      <c r="T10" s="284"/>
+      <c r="U10" s="284"/>
+      <c r="V10" s="284"/>
+      <c r="W10" s="284"/>
+      <c r="X10" s="261"/>
+      <c r="Y10" s="261"/>
+      <c r="Z10" s="261"/>
+      <c r="AA10" s="261"/>
+      <c r="AB10" s="261"/>
+      <c r="AC10" s="261"/>
+      <c r="AD10" s="261"/>
+      <c r="AE10" s="261"/>
+      <c r="AF10" s="261"/>
+      <c r="AG10" s="261"/>
+      <c r="AH10" s="261"/>
+      <c r="AI10" s="261"/>
+      <c r="AJ10" s="261"/>
+      <c r="AK10" s="261"/>
+      <c r="AL10" s="261"/>
+    </row>
+    <row r="11" spans="1:38" x14ac:dyDescent="0.15">
+      <c r="A11" s="285" t="s">
+        <v>302</v>
+      </c>
+      <c r="B11" s="286">
         <f>SUM(B9:B10)</f>
         <v>1</v>
       </c>
-      <c r="C11" s="284">
-        <f t="shared" ref="C11:F11" si="0">SUM(C9:C10)</f>
+      <c r="C11" s="286">
+        <f t="shared" ref="C11:P11" si="0">SUM(C9:C10)</f>
         <v>1</v>
       </c>
-      <c r="D11" s="284">
+      <c r="D11" s="286">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="E11" s="284">
+      <c r="E11" s="286">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F11" s="284">
+      <c r="F11" s="286">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G11" s="284">
-        <f>SUM(B11:F11)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="G11" s="286">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H11" s="286">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I11" s="286">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="J11" s="286">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="K11" s="286">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L11" s="286">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M11" s="286">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="N11" s="286">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="O11" s="286">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="P11" s="286">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Q11" s="286">
+        <f>SUM(B11:P11)</f>
+        <v>15</v>
+      </c>
+      <c r="R11" s="287"/>
+      <c r="S11" s="287"/>
+      <c r="T11" s="287"/>
+      <c r="U11" s="287"/>
+      <c r="V11" s="287"/>
+      <c r="W11" s="287"/>
+    </row>
+    <row r="12" spans="1:38" x14ac:dyDescent="0.15">
       <c r="A12" s="261"/>
-      <c r="B12" s="285"/>
-      <c r="C12" s="285"/>
-      <c r="D12" s="285"/>
-      <c r="E12" s="285"/>
-      <c r="F12" s="285"/>
-      <c r="G12" s="285"/>
-      <c r="H12" s="285"/>
-      <c r="I12" s="285"/>
-      <c r="J12" s="285"/>
-      <c r="K12" s="285"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A13" s="286" t="s">
-        <v>291</v>
-      </c>
-      <c r="B13" s="287"/>
-      <c r="C13" s="287"/>
-      <c r="D13" s="287"/>
-      <c r="F13" s="287"/>
-      <c r="L13" s="263" t="s">
-        <v>292</v>
-      </c>
-      <c r="M13" s="263"/>
-      <c r="N13" s="263"/>
-      <c r="O13" s="263"/>
-      <c r="P13" s="263"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A14" s="288" t="s">
-        <v>293</v>
-      </c>
-      <c r="B14" s="288" t="s">
-        <v>294</v>
-      </c>
-      <c r="C14" s="288" t="s">
-        <v>295</v>
-      </c>
-      <c r="D14" s="288" t="s">
-        <v>296</v>
-      </c>
-      <c r="E14" s="289" t="s">
-        <v>297</v>
-      </c>
-      <c r="F14" s="290"/>
-      <c r="G14" s="291"/>
-      <c r="H14" s="291"/>
-      <c r="I14" s="291"/>
-      <c r="J14" s="292"/>
-      <c r="K14" s="293" t="s">
+      <c r="B12" s="288"/>
+      <c r="C12" s="288"/>
+      <c r="D12" s="288"/>
+      <c r="E12" s="288"/>
+      <c r="F12" s="288"/>
+      <c r="G12" s="288"/>
+      <c r="H12" s="288"/>
+      <c r="I12" s="288"/>
+      <c r="J12" s="288"/>
+      <c r="K12" s="288"/>
+      <c r="L12" s="288"/>
+      <c r="M12" s="288"/>
+      <c r="N12" s="288"/>
+      <c r="O12" s="288"/>
+      <c r="P12" s="288"/>
+      <c r="Q12" s="288"/>
+    </row>
+    <row r="13" spans="1:38" x14ac:dyDescent="0.15">
+      <c r="A13" s="289" t="s">
+        <v>305</v>
+      </c>
+      <c r="B13" s="290"/>
+      <c r="C13" s="290"/>
+      <c r="D13" s="290"/>
+      <c r="F13" s="290"/>
+      <c r="R13" s="263" t="s">
+        <v>306</v>
+      </c>
+      <c r="S13" s="263"/>
+      <c r="T13" s="263"/>
+      <c r="U13" s="263"/>
+      <c r="V13" s="263"/>
+      <c r="W13" s="263"/>
+      <c r="X13" s="263"/>
+      <c r="Y13" s="263"/>
+      <c r="Z13" s="263"/>
+      <c r="AA13" s="263"/>
+      <c r="AB13" s="263"/>
+      <c r="AC13" s="263"/>
+      <c r="AD13" s="263"/>
+      <c r="AE13" s="263"/>
+      <c r="AF13" s="263"/>
+    </row>
+    <row r="14" spans="1:38" x14ac:dyDescent="0.15">
+      <c r="A14" s="291" t="s">
+        <v>307</v>
+      </c>
+      <c r="B14" s="291" t="s">
+        <v>308</v>
+      </c>
+      <c r="C14" s="291" t="s">
+        <v>309</v>
+      </c>
+      <c r="D14" s="291" t="s">
+        <v>310</v>
+      </c>
+      <c r="E14" s="292" t="s">
+        <v>311</v>
+      </c>
+      <c r="F14" s="293"/>
+      <c r="G14" s="294"/>
+      <c r="H14" s="294"/>
+      <c r="I14" s="294"/>
+      <c r="J14" s="295"/>
+      <c r="K14" s="296" t="s">
+        <v>289</v>
+      </c>
+      <c r="R14" s="297" t="s">
+        <v>277</v>
+      </c>
+      <c r="S14" s="297" t="s">
+        <v>278</v>
+      </c>
+      <c r="T14" s="297" t="s">
+        <v>279</v>
+      </c>
+      <c r="U14" s="297" t="s">
+        <v>280</v>
+      </c>
+      <c r="V14" s="297" t="s">
+        <v>281</v>
+      </c>
+      <c r="W14" s="297" t="s">
         <v>282</v>
       </c>
-      <c r="L14" s="294" t="s">
-        <v>277</v>
-      </c>
-      <c r="M14" s="294" t="s">
-        <v>278</v>
-      </c>
-      <c r="N14" s="294" t="s">
-        <v>279</v>
-      </c>
-      <c r="O14" s="294" t="s">
-        <v>280</v>
-      </c>
-      <c r="P14" s="294" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="X14" s="297" t="s">
+        <v>283</v>
+      </c>
+      <c r="Y14" s="297" t="s">
+        <v>284</v>
+      </c>
+      <c r="Z14" s="297" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA14" s="297" t="s">
+        <v>286</v>
+      </c>
+      <c r="AB14" s="297" t="s">
+        <v>287</v>
+      </c>
+      <c r="AC14" s="297" t="s">
+        <v>288</v>
+      </c>
+      <c r="AD14" s="297" t="s">
+        <v>352</v>
+      </c>
+      <c r="AE14" s="297" t="s">
+        <v>353</v>
+      </c>
+      <c r="AF14" s="297" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="15" spans="1:38" x14ac:dyDescent="0.15">
       <c r="A15" s="272" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="297" t="s">
-        <v>301</v>
+        <v>358</v>
+      </c>
+      <c r="B15" s="300" t="s">
+        <v>331</v>
       </c>
       <c r="C15" s="272" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="D15" s="272" t="s">
-        <v>302</v>
-      </c>
-      <c r="E15" s="298" t="s">
-        <v>303</v>
+        <v>359</v>
+      </c>
+      <c r="E15" s="271" t="s">
+        <v>360</v>
       </c>
       <c r="F15" s="271"/>
       <c r="G15" s="271"/>
@@ -3798,50 +4130,88 @@
       <c r="I15" s="271"/>
       <c r="J15" s="271"/>
       <c r="K15" s="272" t="s">
-        <v>300</v>
-      </c>
-      <c r="L15" s="295">
-        <f t="shared" ref="L15:P20" si="1">IF($D15=L$14,1,0)</f>
+        <v>317</v>
+      </c>
+      <c r="R15" s="298">
+        <f t="shared" ref="R15:AF30" si="1">IF($D15=R$14,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S15" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X15" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z15" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA15" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AB15" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AC15" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AD15" s="298">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="M15" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N15" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O15" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P15" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="296" t="str">
+      <c r="AE15" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AG15" s="299" t="str">
         <f>IF(E15&lt;&gt;"",E15,"")</f>
-        <v>レビュー指摘コメントの例。
-自動で挿入される名前とコロンの直後に指摘分類をa～iで書く。
-※レビュー日時を書く場合はコロンの直後に*を書く。</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" ht="40.5" x14ac:dyDescent="0.15">
+        <v>mカテゴリの指摘コメント。</v>
+      </c>
+    </row>
+    <row r="16" spans="1:38" x14ac:dyDescent="0.15">
       <c r="A16" s="272" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="297" t="s">
-        <v>304</v>
+        <v>358</v>
+      </c>
+      <c r="B16" s="300" t="s">
+        <v>346</v>
       </c>
       <c r="C16" s="272" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="D16" s="272" t="s">
-        <v>305</v>
-      </c>
-      <c r="E16" s="298" t="s">
-        <v>306</v>
+        <v>361</v>
+      </c>
+      <c r="E16" s="271" t="s">
+        <v>362</v>
       </c>
       <c r="F16" s="271"/>
       <c r="G16" s="271"/>
@@ -3849,50 +4219,88 @@
       <c r="I16" s="271"/>
       <c r="J16" s="271"/>
       <c r="K16" s="272" t="s">
-        <v>300</v>
-      </c>
-      <c r="L16" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M16" s="295">
+        <v>317</v>
+      </c>
+      <c r="R16" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z16" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA16" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AB16" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AC16" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AD16" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE16" s="298">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="N16" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O16" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P16" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="296" t="str">
+      <c r="AF16" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AG16" s="299" t="str">
         <f>IF(E16&lt;&gt;"",E16,"")</f>
-        <v>対応内容の例。
----
-対応内容はデリミタ（---）の後に記入する。</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" ht="67.5" x14ac:dyDescent="0.15">
+        <v>nカテゴリの指摘コメント。</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A17" s="272" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="297" t="s">
-        <v>307</v>
+        <v>358</v>
+      </c>
+      <c r="B17" s="300" t="s">
+        <v>363</v>
       </c>
       <c r="C17" s="272" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="D17" s="272" t="s">
-        <v>308</v>
-      </c>
-      <c r="E17" s="298" t="s">
-        <v>309</v>
+        <v>364</v>
+      </c>
+      <c r="E17" s="271" t="s">
+        <v>365</v>
       </c>
       <c r="F17" s="271"/>
       <c r="G17" s="271"/>
@@ -3900,52 +4308,88 @@
       <c r="I17" s="271"/>
       <c r="J17" s="271"/>
       <c r="K17" s="272" t="s">
-        <v>310</v>
-      </c>
-      <c r="L17" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M17" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N17" s="295">
+        <v>317</v>
+      </c>
+      <c r="R17" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z17" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA17" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AB17" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AC17" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AD17" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE17" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AF17" s="298">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="O17" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P17" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="296" t="str">
+      <c r="AG17" s="299" t="str">
         <f>IF(E17&lt;&gt;"",E17,"")</f>
-        <v>対応内容を確認し、指摘をクローズする例。
----
-最後の行に「済」と書くと指摘をクローズできる。
-「済」の前にスペースを空けて確認日と確認者を書くこともできる。
-08/02山田 済</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.15">
+        <v>oカテゴリの指摘コメント。</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A18" s="272" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="297" t="s">
-        <v>311</v>
+      <c r="B18" s="300" t="s">
+        <v>313</v>
       </c>
       <c r="C18" s="272" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="D18" s="272" t="s">
-        <v>312</v>
-      </c>
-      <c r="E18" s="271" t="s">
-        <v>313</v>
+        <v>315</v>
+      </c>
+      <c r="E18" s="301" t="s">
+        <v>316</v>
       </c>
       <c r="F18" s="271"/>
       <c r="G18" s="271"/>
@@ -3953,48 +4397,90 @@
       <c r="I18" s="271"/>
       <c r="J18" s="271"/>
       <c r="K18" s="272" t="s">
-        <v>300</v>
-      </c>
-      <c r="L18" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M18" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N18" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O18" s="295">
+        <v>317</v>
+      </c>
+      <c r="R18" s="298">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="P18" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="296" t="str">
+      <c r="S18" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X18" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z18" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA18" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AB18" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AC18" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AD18" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE18" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AG18" s="299" t="str">
         <f>IF(E18&lt;&gt;"",E18,"")</f>
-        <v>機能・仕様誤りの指摘例（カテゴリd）。</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.15">
+        <v>レビュー指摘コメントの例。
+自動で挿入される名前とコロンの直後に指摘分類をa～iで書く。
+※レビュー日時を書く場合はコロンの直後に*を書く。</v>
+      </c>
+    </row>
+    <row r="19" spans="1:33" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A19" s="272" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="297" t="s">
+      <c r="B19" s="300" t="s">
+        <v>318</v>
+      </c>
+      <c r="C19" s="272" t="s">
         <v>314</v>
       </c>
-      <c r="C19" s="272" t="s">
-        <v>299</v>
-      </c>
       <c r="D19" s="272" t="s">
-        <v>315</v>
-      </c>
-      <c r="E19" s="271" t="s">
-        <v>316</v>
+        <v>319</v>
+      </c>
+      <c r="E19" s="301" t="s">
+        <v>320</v>
       </c>
       <c r="F19" s="271"/>
       <c r="G19" s="271"/>
@@ -4002,72 +4488,1057 @@
       <c r="I19" s="271"/>
       <c r="J19" s="271"/>
       <c r="K19" s="272" t="s">
-        <v>300</v>
-      </c>
-      <c r="L19" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M19" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N19" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O19" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P19" s="295">
+        <v>317</v>
+      </c>
+      <c r="R19" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="298">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="Q19" s="296" t="str">
+      <c r="T19" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W19" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X19" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z19" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA19" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AB19" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AC19" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AD19" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE19" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AF19" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AG19" s="299" t="str">
         <f>IF(E19&lt;&gt;"",E19,"")</f>
-        <v>設計・ドキュメント規約違反の指摘例（カテゴリe）。</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A20" s="272"/>
-      <c r="B20" s="272"/>
-      <c r="C20" s="272"/>
-      <c r="D20" s="272"/>
-      <c r="E20" s="271"/>
+        <v>対応内容の例。
+---
+対応内容はデリミタ（---）の後に記入する。</v>
+      </c>
+    </row>
+    <row r="20" spans="1:33" ht="67.5" x14ac:dyDescent="0.15">
+      <c r="A20" s="272" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="300" t="s">
+        <v>321</v>
+      </c>
+      <c r="C20" s="272" t="s">
+        <v>314</v>
+      </c>
+      <c r="D20" s="272" t="s">
+        <v>322</v>
+      </c>
+      <c r="E20" s="301" t="s">
+        <v>323</v>
+      </c>
       <c r="F20" s="271"/>
       <c r="G20" s="271"/>
       <c r="H20" s="271"/>
       <c r="I20" s="271"/>
       <c r="J20" s="271"/>
-      <c r="K20" s="272"/>
-      <c r="L20" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M20" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N20" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O20" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P20" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q20" s="296" t="str">
+      <c r="K20" s="272" t="s">
+        <v>324</v>
+      </c>
+      <c r="R20" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="298">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="U20" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W20" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X20" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z20" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA20" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AB20" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AC20" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AD20" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE20" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AF20" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AG20" s="299" t="str">
         <f>IF(E20&lt;&gt;"",E20,"")</f>
+        <v>対応内容を確認し、指摘をクローズする例。
+---
+最後の行に「済」と書くと指摘をクローズできる。
+「済」の前にスペースを空けて確認日と確認者を書くこともできる。
+08/02山田 済</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="A21" s="272" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="300" t="s">
+        <v>325</v>
+      </c>
+      <c r="C21" s="272" t="s">
+        <v>314</v>
+      </c>
+      <c r="D21" s="272" t="s">
+        <v>326</v>
+      </c>
+      <c r="E21" s="271" t="s">
+        <v>327</v>
+      </c>
+      <c r="F21" s="271"/>
+      <c r="G21" s="271"/>
+      <c r="H21" s="271"/>
+      <c r="I21" s="271"/>
+      <c r="J21" s="271"/>
+      <c r="K21" s="272" t="s">
+        <v>317</v>
+      </c>
+      <c r="R21" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T21" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="298">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="V21" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W21" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X21" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z21" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA21" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AB21" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AC21" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AD21" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE21" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AF21" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AG21" s="299" t="str">
+        <f>IF(E21&lt;&gt;"",E21,"")</f>
+        <v>機能・仕様誤りの指摘例（カテゴリd）。</v>
+      </c>
+    </row>
+    <row r="22" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="A22" s="272" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="300" t="s">
+        <v>328</v>
+      </c>
+      <c r="C22" s="272" t="s">
+        <v>314</v>
+      </c>
+      <c r="D22" s="272" t="s">
+        <v>329</v>
+      </c>
+      <c r="E22" s="271" t="s">
+        <v>330</v>
+      </c>
+      <c r="F22" s="271"/>
+      <c r="G22" s="271"/>
+      <c r="H22" s="271"/>
+      <c r="I22" s="271"/>
+      <c r="J22" s="271"/>
+      <c r="K22" s="272" t="s">
+        <v>317</v>
+      </c>
+      <c r="R22" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T22" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="298">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="W22" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X22" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z22" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA22" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AB22" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AC22" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AD22" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE22" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AF22" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AG22" s="299" t="str">
+        <f>IF(E22&lt;&gt;"",E22,"")</f>
+        <v>設計・ドキュメント規約違反の指摘例（カテゴリe）。</v>
+      </c>
+    </row>
+    <row r="23" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="A23" s="272" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="300" t="s">
+        <v>331</v>
+      </c>
+      <c r="C23" s="272" t="s">
+        <v>314</v>
+      </c>
+      <c r="D23" s="272" t="s">
+        <v>332</v>
+      </c>
+      <c r="E23" s="271" t="s">
+        <v>333</v>
+      </c>
+      <c r="F23" s="271"/>
+      <c r="G23" s="271"/>
+      <c r="H23" s="271"/>
+      <c r="I23" s="271"/>
+      <c r="J23" s="271"/>
+      <c r="K23" s="272" t="s">
+        <v>317</v>
+      </c>
+      <c r="R23" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="298">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="X23" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z23" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA23" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AB23" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AC23" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AD23" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE23" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AF23" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AG23" s="299" t="str">
+        <f>IF(E23&lt;&gt;"",E23,"")</f>
+        <v>記述誤りの指摘例（カテゴリf）。</v>
+      </c>
+    </row>
+    <row r="24" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="A24" s="272" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="300" t="s">
+        <v>334</v>
+      </c>
+      <c r="C24" s="272" t="s">
+        <v>314</v>
+      </c>
+      <c r="D24" s="272" t="s">
+        <v>335</v>
+      </c>
+      <c r="E24" s="271" t="s">
+        <v>336</v>
+      </c>
+      <c r="F24" s="271"/>
+      <c r="G24" s="271"/>
+      <c r="H24" s="271"/>
+      <c r="I24" s="271"/>
+      <c r="J24" s="271"/>
+      <c r="K24" s="272" t="s">
+        <v>317</v>
+      </c>
+      <c r="R24" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W24" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X24" s="298">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Y24" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z24" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA24" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AB24" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AC24" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AD24" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE24" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AF24" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AG24" s="299" t="str">
+        <f>IF(E24&lt;&gt;"",E24,"")</f>
+        <v>疑問点・確認の指摘例（カテゴリg）。</v>
+      </c>
+    </row>
+    <row r="25" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="A25" s="272" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="300" t="s">
+        <v>337</v>
+      </c>
+      <c r="C25" s="272" t="s">
+        <v>314</v>
+      </c>
+      <c r="D25" s="272" t="s">
+        <v>338</v>
+      </c>
+      <c r="E25" s="271" t="s">
+        <v>339</v>
+      </c>
+      <c r="F25" s="271"/>
+      <c r="G25" s="271"/>
+      <c r="H25" s="271"/>
+      <c r="I25" s="271"/>
+      <c r="J25" s="271"/>
+      <c r="K25" s="272" t="s">
+        <v>317</v>
+      </c>
+      <c r="R25" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W25" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X25" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="298">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Z25" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA25" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AB25" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AC25" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AD25" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE25" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AF25" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AG25" s="299" t="str">
+        <f>IF(E25&lt;&gt;"",E25,"")</f>
+        <v>改善要望の指摘例（カテゴリh）。</v>
+      </c>
+    </row>
+    <row r="26" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="A26" s="272" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="300" t="s">
+        <v>340</v>
+      </c>
+      <c r="C26" s="272" t="s">
+        <v>314</v>
+      </c>
+      <c r="D26" s="272" t="s">
+        <v>341</v>
+      </c>
+      <c r="E26" s="271" t="s">
+        <v>342</v>
+      </c>
+      <c r="F26" s="271"/>
+      <c r="G26" s="271"/>
+      <c r="H26" s="271"/>
+      <c r="I26" s="271"/>
+      <c r="J26" s="271"/>
+      <c r="K26" s="272" t="s">
+        <v>317</v>
+      </c>
+      <c r="R26" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S26" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T26" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X26" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z26" s="298">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AA26" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AB26" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AC26" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AD26" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE26" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AF26" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AG26" s="299" t="str">
+        <f>IF(E26&lt;&gt;"",E26,"")</f>
+        <v>仕様変更の指摘例（カテゴリi）。</v>
+      </c>
+    </row>
+    <row r="27" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="A27" s="272" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="300" t="s">
+        <v>343</v>
+      </c>
+      <c r="C27" s="272" t="s">
+        <v>314</v>
+      </c>
+      <c r="D27" s="272" t="s">
+        <v>344</v>
+      </c>
+      <c r="E27" s="271" t="s">
+        <v>345</v>
+      </c>
+      <c r="F27" s="271"/>
+      <c r="G27" s="271"/>
+      <c r="H27" s="271"/>
+      <c r="I27" s="271"/>
+      <c r="J27" s="271"/>
+      <c r="K27" s="272" t="s">
+        <v>317</v>
+      </c>
+      <c r="R27" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T27" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X27" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z27" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA27" s="298">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AB27" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AC27" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AD27" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE27" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AF27" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AG27" s="299" t="str">
+        <f>IF(E27&lt;&gt;"",E27,"")</f>
+        <v>テスト項目漏れの指摘例（カテゴリj）。</v>
+      </c>
+    </row>
+    <row r="28" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="A28" s="272" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="300" t="s">
+        <v>346</v>
+      </c>
+      <c r="C28" s="272" t="s">
+        <v>314</v>
+      </c>
+      <c r="D28" s="272" t="s">
+        <v>347</v>
+      </c>
+      <c r="E28" s="271" t="s">
+        <v>348</v>
+      </c>
+      <c r="F28" s="271"/>
+      <c r="G28" s="271"/>
+      <c r="H28" s="271"/>
+      <c r="I28" s="271"/>
+      <c r="J28" s="271"/>
+      <c r="K28" s="272" t="s">
+        <v>317</v>
+      </c>
+      <c r="R28" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T28" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X28" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z28" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA28" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AB28" s="298">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AC28" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AD28" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE28" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AF28" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AG28" s="299" t="str">
+        <f>IF(E28&lt;&gt;"",E28,"")</f>
+        <v>テスト漏れの指摘例（カテゴリk）。</v>
+      </c>
+    </row>
+    <row r="29" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="A29" s="272" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="300" t="s">
+        <v>349</v>
+      </c>
+      <c r="C29" s="272" t="s">
+        <v>314</v>
+      </c>
+      <c r="D29" s="272" t="s">
+        <v>350</v>
+      </c>
+      <c r="E29" s="271" t="s">
+        <v>351</v>
+      </c>
+      <c r="F29" s="271"/>
+      <c r="G29" s="271"/>
+      <c r="H29" s="271"/>
+      <c r="I29" s="271"/>
+      <c r="J29" s="271"/>
+      <c r="K29" s="272" t="s">
+        <v>317</v>
+      </c>
+      <c r="R29" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S29" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T29" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U29" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W29" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X29" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y29" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z29" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA29" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AB29" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AC29" s="298">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AD29" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE29" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AF29" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AG29" s="299" t="str">
+        <f>IF(E29&lt;&gt;"",E29,"")</f>
+        <v>その他の指摘例（カテゴリl）。</v>
+      </c>
+    </row>
+    <row r="30" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="A30" s="272"/>
+      <c r="B30" s="272"/>
+      <c r="C30" s="272"/>
+      <c r="D30" s="272"/>
+      <c r="E30" s="271"/>
+      <c r="F30" s="271"/>
+      <c r="G30" s="271"/>
+      <c r="H30" s="271"/>
+      <c r="I30" s="271"/>
+      <c r="J30" s="271"/>
+      <c r="K30" s="272"/>
+      <c r="R30" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S30" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T30" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W30" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X30" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y30" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z30" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA30" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AB30" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AC30" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AD30" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE30" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AF30" s="298">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AG30" s="299" t="str">
+        <f>IF(E30&lt;&gt;"",E30,"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="18">
+    <mergeCell ref="E28:J28"/>
+    <mergeCell ref="E29:J29"/>
+    <mergeCell ref="E30:J30"/>
+    <mergeCell ref="E22:J22"/>
+    <mergeCell ref="E23:J23"/>
+    <mergeCell ref="E24:J24"/>
+    <mergeCell ref="E25:J25"/>
+    <mergeCell ref="E26:J26"/>
+    <mergeCell ref="E27:J27"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="E15:J15"/>
@@ -4076,32 +5547,43 @@
     <mergeCell ref="E18:J18"/>
     <mergeCell ref="E19:J19"/>
     <mergeCell ref="E20:J20"/>
+    <mergeCell ref="E21:J21"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
-  <conditionalFormatting sqref="A15:K20">
+  <conditionalFormatting sqref="A15:K30">
     <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
       <formula>$K15="済"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:K20" xr:uid="{FB5DD73F-BD57-468A-A168-1017C7BB9723}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:Q30" xr:uid="{9BE6D98D-84E9-4E2A-BB49-89ED8A7523A0}">
       <formula1>"未,済"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="B15" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{F2817F04-80F9-46EA-BC89-FFDC15101836}"/>
-    <hyperlink ref="B16" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{C44455BA-9603-4989-936F-623E9E021CA0}"/>
-    <hyperlink ref="B17" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{AA22293C-FBAD-49F5-8A67-31EE94C898C0}"/>
-    <hyperlink ref="B18" location="'2. WA1020101(プロジェクト登録画面)'!$E$63" display="'2. WA1020101(プロジェクト登録画面)'!$E$63" xr:uid="{646675C6-86EE-44A9-A9E2-9A321BD06BB8}"/>
-    <hyperlink ref="B19" location="'2. WA1020101(プロジェクト登録画面)'!$E$64" display="'2. WA1020101(プロジェクト登録画面)'!$E$64" xr:uid="{F99A69A7-C471-4CD4-9C57-8E91F51D8597}"/>
+    <hyperlink ref="B15" location="'変更履歴'!$E$65" display="'変更履歴'!$E$65" xr:uid="{27ACB1D0-C8C3-4F37-9B2B-C0843B36D966}"/>
+    <hyperlink ref="B16" location="'変更履歴'!$E$70" display="'変更履歴'!$E$70" xr:uid="{DAEDF2CD-4EEB-4AD3-B926-FAD03177CB31}"/>
+    <hyperlink ref="B17" location="'変更履歴'!$E$75" display="'変更履歴'!$E$75" xr:uid="{83C3B087-4FD2-43D8-9115-0FB62BE63DF9}"/>
+    <hyperlink ref="B18" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{D8075166-8D6B-4457-A3C7-A83865F3219C}"/>
+    <hyperlink ref="B19" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{F778890E-60CF-4842-89B4-E3325807C923}"/>
+    <hyperlink ref="B20" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{A36686D8-BA15-4DDC-853F-780E99886FD0}"/>
+    <hyperlink ref="B21" location="'2. WA1020101(プロジェクト登録画面)'!$E$63" display="'2. WA1020101(プロジェクト登録画面)'!$E$63" xr:uid="{5897464C-D7FB-436F-AFCE-15F36843FEF8}"/>
+    <hyperlink ref="B22" location="'2. WA1020101(プロジェクト登録画面)'!$E$64" display="'2. WA1020101(プロジェクト登録画面)'!$E$64" xr:uid="{810C0EE3-0C39-4084-BA07-8CC3023D21EA}"/>
+    <hyperlink ref="B23" location="'2. WA1020101(プロジェクト登録画面)'!$E$65" display="'2. WA1020101(プロジェクト登録画面)'!$E$65" xr:uid="{D60A4E58-E1FA-41BD-B942-6D308C4877A5}"/>
+    <hyperlink ref="B24" location="'2. WA1020101(プロジェクト登録画面)'!$E$66" display="'2. WA1020101(プロジェクト登録画面)'!$E$66" xr:uid="{66C92CF3-07F8-4677-A9A6-F0EA7F228E61}"/>
+    <hyperlink ref="B25" location="'2. WA1020101(プロジェクト登録画面)'!$E$67" display="'2. WA1020101(プロジェクト登録画面)'!$E$67" xr:uid="{7F2D3476-9348-493B-B1ED-8C73DBD5D2D9}"/>
+    <hyperlink ref="B26" location="'2. WA1020101(プロジェクト登録画面)'!$E$68" display="'2. WA1020101(プロジェクト登録画面)'!$E$68" xr:uid="{71D916B6-B133-4E6D-849B-E1AD1EA0F47F}"/>
+    <hyperlink ref="B27" location="'2. WA1020101(プロジェクト登録画面)'!$E$69" display="'2. WA1020101(プロジェクト登録画面)'!$E$69" xr:uid="{14EE1DBF-D8A9-4425-95F2-9369B7902476}"/>
+    <hyperlink ref="B28" location="'2. WA1020101(プロジェクト登録画面)'!$E$70" display="'2. WA1020101(プロジェクト登録画面)'!$E$70" xr:uid="{132C7DCC-61EA-4A52-909A-2C6375D03A9B}"/>
+    <hyperlink ref="B29" location="'2. WA1020101(プロジェクト登録画面)'!$E$71" display="'2. WA1020101(プロジェクト登録画面)'!$E$71" xr:uid="{D71C0125-1F0A-4633-B113-0F675530C0AE}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
-  <pageSetup paperSize="9" scale="86" orientation="landscape" verticalDpi="200" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="55" orientation="landscape" verticalDpi="200" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet3">
     <pageSetUpPr fitToPage="1"/>
@@ -4781,12 +6263,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN35"/>
+  <dimension ref="A1:AN75"/>
   <sheetFormatPr defaultColWidth="4.83203125" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:40" s="11" customFormat="1" x14ac:dyDescent="0.15">
@@ -6153,7 +7635,9 @@
       <c r="AI33" s="163"/>
     </row>
     <row r="34" spans="1:35" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="35" spans="1:35" x14ac:dyDescent="0.15"/>
+    <row r="65" spans="5:5" x14ac:dyDescent="0.15"/>
+    <row r="70" spans="5:5" x14ac:dyDescent="0.15"/>
+    <row r="75" spans="5:5" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="179">
     <mergeCell ref="Q33:AE33"/>
@@ -6344,7 +7828,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet4">
     <pageSetUpPr fitToPage="1"/>
@@ -7090,7 +8574,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet5">
     <pageSetUpPr fitToPage="1"/>
@@ -7596,7 +9080,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet7">
     <pageSetUpPr fitToPage="1"/>
@@ -11897,7 +13381,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet8">
     <pageSetUpPr fitToPage="1"/>
@@ -15416,7 +16900,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
@@ -16586,4 +18070,143 @@
     <brk id="33" max="34" man="1"/>
   </rowBreaks>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <sheetPr codeName="Sheet6">
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="21" customWidth="1"/>
+    <col min="2" max="2" width="30.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A1" s="53" t="s">
+        <v>249</v>
+      </c>
+      <c r="B1" s="54" t="s">
+        <v>250</v>
+      </c>
+      <c r="C1" s="55" t="s">
+        <v>251</v>
+      </c>
+      <c r="D1" s="55" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A2" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="56" t="s">
+        <v>252</v>
+      </c>
+      <c r="C2" s="57" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="52" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A3" s="52" t="s">
+        <v>106</v>
+      </c>
+      <c r="B3" s="56" t="s">
+        <v>253</v>
+      </c>
+      <c r="C3" s="52" t="s">
+        <v>134</v>
+      </c>
+      <c r="D3" s="52" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A4" s="52" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" s="52" t="s">
+        <v>254</v>
+      </c>
+      <c r="C4" s="52" t="s">
+        <v>255</v>
+      </c>
+      <c r="D4" s="52" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A5" s="52" t="s">
+        <v>256</v>
+      </c>
+      <c r="B5" s="52" t="s">
+        <v>257</v>
+      </c>
+      <c r="C5" s="52" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A6" s="52" t="s">
+        <v>122</v>
+      </c>
+      <c r="C6" s="52" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A7" s="52" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="52" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A8" s="52" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A9" s="52" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A10" s="52" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A11" s="52" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A12" s="52" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A13" s="52" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A14" s="52" t="s">
+        <v>264</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="10"/>
+  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+</worksheet>
 </file>
--- a/doctool/test/auto/scenario32/システム機能設計書_サンプル_S32_expected.xlsx
+++ b/doctool/test/auto/scenario32/システム機能設計書_サンプル_S32_expected.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJ\01.Nablarch\repo\review-support-tool\doctool\test\temp_dir\scenario31\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJ\01.Nablarch\repo\review-support-tool\doctool\test\temp_dir\scenario32\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5EAFB83-60F4-4ADD-B58C-E7C5C28DB933}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54117A3E-35D1-4109-AD0E-E79E9F88E24F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="38700" windowHeight="15345" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="レビュー結果1回目" sheetId="11" r:id="rId1"/>
@@ -1429,7 +1429,7 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>システム機能設計書_サンプル_S31</t>
+    <t>システム機能設計書_サンプル_S32</t>
   </si>
   <si>
     <t>B5</t>
@@ -3529,7 +3529,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AD5E0D3-F4C6-4381-9644-6AB1EF741361}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BD4C5FB-C2B6-4244-8D95-27A743F7E9D2}">
   <sheetPr codeName="SheetTemplate">
     <tabColor indexed="44"/>
     <pageSetUpPr fitToPage="1"/>
@@ -5556,26 +5556,26 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:Q30" xr:uid="{9BE6D98D-84E9-4E2A-BB49-89ED8A7523A0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:Q30" xr:uid="{AF6326DB-D7BD-4743-A001-01CA722E30DA}">
       <formula1>"未,済"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="B15" location="'変更履歴'!$E$65" display="'変更履歴'!$E$65" xr:uid="{27ACB1D0-C8C3-4F37-9B2B-C0843B36D966}"/>
-    <hyperlink ref="B16" location="'変更履歴'!$E$70" display="'変更履歴'!$E$70" xr:uid="{DAEDF2CD-4EEB-4AD3-B926-FAD03177CB31}"/>
-    <hyperlink ref="B17" location="'変更履歴'!$E$75" display="'変更履歴'!$E$75" xr:uid="{83C3B087-4FD2-43D8-9115-0FB62BE63DF9}"/>
-    <hyperlink ref="B18" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{D8075166-8D6B-4457-A3C7-A83865F3219C}"/>
-    <hyperlink ref="B19" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{F778890E-60CF-4842-89B4-E3325807C923}"/>
-    <hyperlink ref="B20" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{A36686D8-BA15-4DDC-853F-780E99886FD0}"/>
-    <hyperlink ref="B21" location="'2. WA1020101(プロジェクト登録画面)'!$E$63" display="'2. WA1020101(プロジェクト登録画面)'!$E$63" xr:uid="{5897464C-D7FB-436F-AFCE-15F36843FEF8}"/>
-    <hyperlink ref="B22" location="'2. WA1020101(プロジェクト登録画面)'!$E$64" display="'2. WA1020101(プロジェクト登録画面)'!$E$64" xr:uid="{810C0EE3-0C39-4084-BA07-8CC3023D21EA}"/>
-    <hyperlink ref="B23" location="'2. WA1020101(プロジェクト登録画面)'!$E$65" display="'2. WA1020101(プロジェクト登録画面)'!$E$65" xr:uid="{D60A4E58-E1FA-41BD-B942-6D308C4877A5}"/>
-    <hyperlink ref="B24" location="'2. WA1020101(プロジェクト登録画面)'!$E$66" display="'2. WA1020101(プロジェクト登録画面)'!$E$66" xr:uid="{66C92CF3-07F8-4677-A9A6-F0EA7F228E61}"/>
-    <hyperlink ref="B25" location="'2. WA1020101(プロジェクト登録画面)'!$E$67" display="'2. WA1020101(プロジェクト登録画面)'!$E$67" xr:uid="{7F2D3476-9348-493B-B1ED-8C73DBD5D2D9}"/>
-    <hyperlink ref="B26" location="'2. WA1020101(プロジェクト登録画面)'!$E$68" display="'2. WA1020101(プロジェクト登録画面)'!$E$68" xr:uid="{71D916B6-B133-4E6D-849B-E1AD1EA0F47F}"/>
-    <hyperlink ref="B27" location="'2. WA1020101(プロジェクト登録画面)'!$E$69" display="'2. WA1020101(プロジェクト登録画面)'!$E$69" xr:uid="{14EE1DBF-D8A9-4425-95F2-9369B7902476}"/>
-    <hyperlink ref="B28" location="'2. WA1020101(プロジェクト登録画面)'!$E$70" display="'2. WA1020101(プロジェクト登録画面)'!$E$70" xr:uid="{132C7DCC-61EA-4A52-909A-2C6375D03A9B}"/>
-    <hyperlink ref="B29" location="'2. WA1020101(プロジェクト登録画面)'!$E$71" display="'2. WA1020101(プロジェクト登録画面)'!$E$71" xr:uid="{D71C0125-1F0A-4633-B113-0F675530C0AE}"/>
+    <hyperlink ref="B15" location="'変更履歴'!$E$65" display="'変更履歴'!$E$65" xr:uid="{F7A5742C-B62B-46F9-A63A-4ABCC295DE4B}"/>
+    <hyperlink ref="B16" location="'変更履歴'!$E$70" display="'変更履歴'!$E$70" xr:uid="{87F6401E-3C5A-4FA5-B72D-88CC704119B7}"/>
+    <hyperlink ref="B17" location="'変更履歴'!$E$75" display="'変更履歴'!$E$75" xr:uid="{1A7727D4-DAE9-4D7F-880B-A1D1E7D66E91}"/>
+    <hyperlink ref="B18" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{005E8B41-3822-4802-80CE-DB0830422216}"/>
+    <hyperlink ref="B19" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{F8F9352E-29E2-46EA-A37F-C23801ED2153}"/>
+    <hyperlink ref="B20" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{F5FBA9C7-AC8A-4C31-8821-5E5F29C709CB}"/>
+    <hyperlink ref="B21" location="'2. WA1020101(プロジェクト登録画面)'!$E$63" display="'2. WA1020101(プロジェクト登録画面)'!$E$63" xr:uid="{A5082D86-C815-453F-B085-AD1B0C253894}"/>
+    <hyperlink ref="B22" location="'2. WA1020101(プロジェクト登録画面)'!$E$64" display="'2. WA1020101(プロジェクト登録画面)'!$E$64" xr:uid="{2F64AE04-BE13-4735-A266-555B2287E860}"/>
+    <hyperlink ref="B23" location="'2. WA1020101(プロジェクト登録画面)'!$E$65" display="'2. WA1020101(プロジェクト登録画面)'!$E$65" xr:uid="{FDC06E8D-6D0A-433C-8D71-FD3FE9F09428}"/>
+    <hyperlink ref="B24" location="'2. WA1020101(プロジェクト登録画面)'!$E$66" display="'2. WA1020101(プロジェクト登録画面)'!$E$66" xr:uid="{BF399DFE-A168-4E8E-9842-58CCB731D294}"/>
+    <hyperlink ref="B25" location="'2. WA1020101(プロジェクト登録画面)'!$E$67" display="'2. WA1020101(プロジェクト登録画面)'!$E$67" xr:uid="{65B6E352-0A5B-42A2-B429-88413FC01A74}"/>
+    <hyperlink ref="B26" location="'2. WA1020101(プロジェクト登録画面)'!$E$68" display="'2. WA1020101(プロジェクト登録画面)'!$E$68" xr:uid="{CE4C32F6-6653-448B-9987-BB6D7AC49568}"/>
+    <hyperlink ref="B27" location="'2. WA1020101(プロジェクト登録画面)'!$E$69" display="'2. WA1020101(プロジェクト登録画面)'!$E$69" xr:uid="{17140AC9-8899-4342-A95E-97AE100E92A2}"/>
+    <hyperlink ref="B28" location="'2. WA1020101(プロジェクト登録画面)'!$E$70" display="'2. WA1020101(プロジェクト登録画面)'!$E$70" xr:uid="{781ED942-DE20-4099-AAE6-9E52D3F600BD}"/>
+    <hyperlink ref="B29" location="'2. WA1020101(プロジェクト登録画面)'!$E$71" display="'2. WA1020101(プロジェクト登録画面)'!$E$71" xr:uid="{C45CA868-B83B-4756-900E-15761A0E15CB}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
   <pageSetup paperSize="9" scale="55" orientation="landscape" verticalDpi="200" r:id="rId1"/>
